--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008545626218323586</v>
       </c>
       <c r="C2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>51786492</v>
+        <v>3859949</v>
       </c>
       <c r="L2" t="n">
-        <v>26924693</v>
+        <v>1630503</v>
       </c>
       <c r="M2" t="n">
-        <v>6235141</v>
+        <v>324286</v>
       </c>
       <c r="N2" t="n">
-        <v>250506</v>
+        <v>6611</v>
       </c>
       <c r="O2" t="n">
-        <v>3602596</v>
+        <v>172143</v>
       </c>
       <c r="P2" t="n">
-        <v>1333606</v>
+        <v>33757</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999889135360718</v>
+        <v>0.9999952912330627</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8242475986480713</v>
+        <v>0.7114532589912415</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6867137551307678</v>
+        <v>0.5152195692062378</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5984489917755127</v>
+        <v>0.3739611208438873</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2029456794261932</v>
+        <v>0.04853107407689095</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6597989797592163</v>
+        <v>0.4115378856658936</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7917230129241943</v>
+        <v>0.5841119885444641</v>
       </c>
       <c r="X2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558068513870239</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117310047149658</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579899072647095</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614375710487366</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019421935081482</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002047782815014169</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>51786492</v>
+        <v>3859949</v>
       </c>
       <c r="E3" t="n">
-        <v>8263032</v>
+        <v>1036584</v>
       </c>
       <c r="F3" t="n">
-        <v>311810</v>
+        <v>64584</v>
       </c>
       <c r="G3" t="n">
-        <v>23606</v>
+        <v>5332</v>
       </c>
       <c r="H3" t="n">
-        <v>20782</v>
+        <v>5895</v>
       </c>
       <c r="I3" t="n">
-        <v>1414</v>
+        <v>282</v>
       </c>
       <c r="J3" t="n">
-        <v>120834597</v>
+        <v>10069590</v>
       </c>
       <c r="K3" t="n">
-        <v>125542474</v>
+        <v>9877872</v>
       </c>
       <c r="L3" t="n">
-        <v>145061986</v>
+        <v>11528374</v>
       </c>
       <c r="M3" t="n">
-        <v>181552323</v>
+        <v>14926996</v>
       </c>
       <c r="N3" t="n">
-        <v>194932465</v>
+        <v>16196153</v>
       </c>
       <c r="O3" t="n">
-        <v>189007173</v>
+        <v>15656729</v>
       </c>
       <c r="P3" t="n">
-        <v>194318576</v>
+        <v>16197915</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8572899103164673</v>
+        <v>0.7762383222579956</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6791159510612488</v>
+        <v>0.4862161576747894</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5539401769638062</v>
+        <v>0.3427517414093018</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2328791469335556</v>
+        <v>0.07326344400644302</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5879600048065186</v>
+        <v>0.3354816138744354</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5741879343986511</v>
+        <v>0.1739603132009506</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2382014</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102565</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82163</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120835440</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>133910484</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>153853413</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184139493</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>195552500</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190264326</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>194510227</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957497239112854</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097340106964111</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569492101669312</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.660748302936554</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012896418571472</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03221459809678776</v>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>10129080</v>
+        <v>1387185</v>
       </c>
       <c r="E4" t="n">
-        <v>26924693</v>
+        <v>1630503</v>
       </c>
       <c r="F4" t="n">
-        <v>2191557</v>
+        <v>267769</v>
       </c>
       <c r="G4" t="n">
-        <v>136712</v>
+        <v>23680</v>
       </c>
       <c r="H4" t="n">
-        <v>241210</v>
+        <v>41542</v>
       </c>
       <c r="I4" t="n">
-        <v>23336</v>
+        <v>2769</v>
       </c>
       <c r="J4" t="n">
-        <v>843</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>11042315</v>
+        <v>1565494</v>
       </c>
       <c r="L4" t="n">
-        <v>12283335</v>
+        <v>1534173</v>
       </c>
       <c r="M4" t="n">
-        <v>4183694</v>
+        <v>542879</v>
       </c>
       <c r="N4" t="n">
-        <v>983844</v>
+        <v>129611</v>
       </c>
       <c r="O4" t="n">
-        <v>1857546</v>
+        <v>246149</v>
       </c>
       <c r="P4" t="n">
-        <v>350829</v>
+        <v>24035</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999944567680359</v>
+        <v>0.9999976754188538</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8404440879821777</v>
+        <v>0.7424351572990417</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6828937530517578</v>
+        <v>0.5002978444099426</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5753350257873535</v>
+        <v>0.3576769232749939</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2168844640254974</v>
+        <v>0.05838610231876373</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6218114495277405</v>
+        <v>0.3696379959583282</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6656331419944763</v>
+        <v>0.2680807709693909</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2497781</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>999552</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>66772</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13821</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2674305</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3491908</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1596524</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>363809</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600393</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566512703895569</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107314348220825</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574692010879517</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610927581787109</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016157984733582</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>657522</v>
+        <v>131288</v>
       </c>
       <c r="E5" t="n">
-        <v>3232585</v>
+        <v>362670</v>
       </c>
       <c r="F5" t="n">
-        <v>6235141</v>
+        <v>324286</v>
       </c>
       <c r="G5" t="n">
-        <v>304136</v>
+        <v>35557</v>
       </c>
       <c r="H5" t="n">
-        <v>747200</v>
+        <v>84182</v>
       </c>
       <c r="I5" t="n">
-        <v>79341</v>
+        <v>8140</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8620719</v>
+        <v>1112685</v>
       </c>
       <c r="L5" t="n">
-        <v>12721986</v>
+        <v>1722950</v>
       </c>
       <c r="M5" t="n">
-        <v>5020842</v>
+        <v>621839</v>
       </c>
       <c r="N5" t="n">
-        <v>825185</v>
+        <v>83625</v>
       </c>
       <c r="O5" t="n">
-        <v>2524685</v>
+        <v>340979</v>
       </c>
       <c r="P5" t="n">
-        <v>988989</v>
+        <v>160293</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999957084655762</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9001836180686951</v>
+        <v>0.8368555903434753</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8730642795562744</v>
+        <v>0.8015885353088379</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9532745480537415</v>
+        <v>0.9290498495101929</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908167123794556</v>
+        <v>0.9870104789733887</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9777542948722839</v>
+        <v>0.9642344117164612</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931986331939697</v>
+        <v>0.9887714385986328</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97322</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1034594</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>119997</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>350660</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2567472</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3578747</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1610177</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>364930</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604826</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733909368515015</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641069173812866</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837216734886169</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963006377220154</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.99388188123703</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983799457550049</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>137</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>179011</v>
+        <v>23165</v>
       </c>
       <c r="E6" t="n">
-        <v>229188</v>
+        <v>25859</v>
       </c>
       <c r="F6" t="n">
-        <v>302903</v>
+        <v>24998</v>
       </c>
       <c r="G6" t="n">
-        <v>250506</v>
+        <v>6611</v>
       </c>
       <c r="H6" t="n">
-        <v>103212</v>
+        <v>8917</v>
       </c>
       <c r="I6" t="n">
-        <v>10734</v>
+        <v>679</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78611</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64601</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>131879</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84061</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>71260</v>
+        <v>21594</v>
       </c>
       <c r="E7" t="n">
-        <v>507154</v>
+        <v>96813</v>
       </c>
       <c r="F7" t="n">
-        <v>1252671</v>
+        <v>158020</v>
       </c>
       <c r="G7" t="n">
-        <v>457474</v>
+        <v>52383</v>
       </c>
       <c r="H7" t="n">
-        <v>3602596</v>
+        <v>172143</v>
       </c>
       <c r="I7" t="n">
-        <v>236004</v>
+        <v>12165</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9726</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358547</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91683</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>360</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5442</v>
+        <v>2262</v>
       </c>
       <c r="E8" t="n">
-        <v>51376</v>
+        <v>12247</v>
       </c>
       <c r="F8" t="n">
-        <v>124753</v>
+        <v>27508</v>
       </c>
       <c r="G8" t="n">
-        <v>61916</v>
+        <v>12659</v>
       </c>
       <c r="H8" t="n">
-        <v>745142</v>
+        <v>105613</v>
       </c>
       <c r="I8" t="n">
-        <v>1333606</v>
+        <v>33757</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
